--- a/artfynd/A 15611-2024 artfynd.xlsx
+++ b/artfynd/A 15611-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,45 +680,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120018592</v>
+        <v>137165388</v>
       </c>
       <c r="B2" t="n">
-        <v>80432</v>
+        <v>79485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norråsbäcken, Jmt</t>
+          <t>Nybräntberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542541</v>
+        <v>542997</v>
       </c>
       <c r="R2" t="n">
-        <v>7010135</v>
+        <v>7010092</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,13 +780,335 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137165388</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137165389</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79485</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Nybräntberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>542974</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7010109</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137165389</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120018592</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norråsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>542541</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7010135</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/120018592</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137165391</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nybräntberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>542990</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7010100</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137165391</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15611-2024 artfynd.xlsx
+++ b/artfynd/A 15611-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137165388</v>
       </c>
       <c r="B2" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137165389</v>
       </c>
       <c r="B3" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15611-2024 artfynd.xlsx
+++ b/artfynd/A 15611-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137165388</v>
       </c>
       <c r="B2" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137165389</v>
       </c>
       <c r="B3" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137165391</v>
       </c>
       <c r="B5" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15611-2024 artfynd.xlsx
+++ b/artfynd/A 15611-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137165388</v>
       </c>
       <c r="B2" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137165389</v>
       </c>
       <c r="B3" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137165391</v>
       </c>
       <c r="B5" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15611-2024 artfynd.xlsx
+++ b/artfynd/A 15611-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137165388</v>
       </c>
       <c r="B2" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137165389</v>
       </c>
       <c r="B3" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137165391</v>
       </c>
       <c r="B5" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15611-2024 artfynd.xlsx
+++ b/artfynd/A 15611-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137165388</v>
       </c>
       <c r="B2" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137165389</v>
       </c>
       <c r="B3" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137165391</v>
       </c>
       <c r="B5" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15611-2024 artfynd.xlsx
+++ b/artfynd/A 15611-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137165388</v>
       </c>
       <c r="B2" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137165389</v>
       </c>
       <c r="B3" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137165391</v>
       </c>
       <c r="B5" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15611-2024 artfynd.xlsx
+++ b/artfynd/A 15611-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137165388</v>
       </c>
       <c r="B2" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137165389</v>
       </c>
       <c r="B3" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15611-2024 artfynd.xlsx
+++ b/artfynd/A 15611-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137165388</v>
       </c>
       <c r="B2" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137165389</v>
       </c>
       <c r="B3" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15611-2024 artfynd.xlsx
+++ b/artfynd/A 15611-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137165388</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137165389</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15611-2024 artfynd.xlsx
+++ b/artfynd/A 15611-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137165388</v>
       </c>
       <c r="B2" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137165389</v>
       </c>
       <c r="B3" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137165391</v>
       </c>
       <c r="B5" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
